--- a/data_execl/base_data/ActivityGroups.xlsx
+++ b/data_execl/base_data/ActivityGroups.xlsx
@@ -1,25 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\X1\Trunk\data_execl\base_data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9452D8D7-0EFA-4CA2-82E5-B1581646A022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15525" xr2:uid="{24496E0C-FA7A-4D51-8D25-21B59E9160E6}"/>
+    <workbookView windowHeight="16160"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityGroups" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="155">
   <si>
     <t>Id</t>
   </si>
@@ -256,6 +247,9 @@
     <t>X1_zhucheng_chongzhi</t>
   </si>
   <si>
+    <t>2#18</t>
+  </si>
+  <si>
     <t>1#5#3</t>
   </si>
   <si>
@@ -454,6 +448,9 @@
     <t>X1_zhucheng_chaozhijijin</t>
   </si>
   <si>
+    <t>2#21</t>
+  </si>
+  <si>
     <t>X1_zhucheng_tiantianzengli</t>
   </si>
   <si>
@@ -476,9 +473,6 @@
   </si>
   <si>
     <t>X1_zhucheng_xianshizhekou</t>
-  </si>
-  <si>
-    <t>2#18</t>
   </si>
   <si>
     <t>X1_zhucheng_Gonghuizhan</t>
@@ -511,33 +505,368 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -545,9 +874,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -559,17 +1130,61 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -618,7 +1233,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -651,26 +1266,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -703,23 +1301,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -861,21 +1442,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E91857-CFC5-4C3B-AB51-AEC656BC25A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:W145"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:23">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -943,7 +1519,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:23">
       <c r="B2" t="s">
         <v>22</v>
       </c>
@@ -1011,7 +1587,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:23">
       <c r="B3">
         <v>3</v>
       </c>
@@ -1079,7 +1655,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="4" ht="168" spans="2:23">
       <c r="B4" t="s">
         <v>27</v>
       </c>
@@ -1147,7 +1723,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23">
       <c r="A5" t="s">
         <v>49</v>
       </c>
@@ -1194,17 +1770,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:23">
       <c r="B8">
         <v>3</v>
       </c>
@@ -1245,7 +1821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:23">
       <c r="B9">
         <v>14</v>
       </c>
@@ -1286,7 +1862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:23">
       <c r="B10">
         <v>39</v>
       </c>
@@ -1327,7 +1903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:23">
       <c r="B11">
         <v>40</v>
       </c>
@@ -1368,7 +1944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:23">
       <c r="B12">
         <v>57</v>
       </c>
@@ -1409,7 +1985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:23">
       <c r="B13">
         <v>58</v>
       </c>
@@ -1450,7 +2026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:23">
       <c r="B14">
         <v>64</v>
       </c>
@@ -1497,7 +2073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:23">
       <c r="B15">
         <v>7</v>
       </c>
@@ -1538,7 +2114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:23">
       <c r="B16">
         <v>11</v>
       </c>
@@ -1579,7 +2155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:23">
       <c r="B17">
         <v>12</v>
       </c>
@@ -1620,7 +2196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:23">
       <c r="B18">
         <v>90</v>
       </c>
@@ -1655,7 +2231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:23">
       <c r="B19">
         <v>63</v>
       </c>
@@ -1708,7 +2284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:23">
       <c r="B20">
         <v>1</v>
       </c>
@@ -1752,7 +2328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:23">
       <c r="B21">
         <v>1500</v>
       </c>
@@ -1796,7 +2372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:23">
       <c r="B22">
         <v>4</v>
       </c>
@@ -1840,7 +2416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:23">
       <c r="B23">
         <v>209</v>
       </c>
@@ -1884,7 +2460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:23">
       <c r="B24">
         <v>10</v>
       </c>
@@ -1928,7 +2504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:23">
       <c r="B25">
         <v>801</v>
       </c>
@@ -1972,7 +2548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:23">
       <c r="B26">
         <v>17</v>
       </c>
@@ -2016,7 +2592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:23">
       <c r="B27">
         <v>6</v>
       </c>
@@ -2057,13 +2633,13 @@
         <v>412</v>
       </c>
       <c r="S27" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="W27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:23">
       <c r="B28">
         <v>62</v>
       </c>
@@ -2113,13 +2689,13 @@
         <v>56</v>
       </c>
       <c r="V28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="W28">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:23">
       <c r="B29">
         <v>59</v>
       </c>
@@ -2169,13 +2745,13 @@
         <v>56</v>
       </c>
       <c r="V29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W29">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:23">
       <c r="B30">
         <v>67</v>
       </c>
@@ -2219,13 +2795,13 @@
         <v>54</v>
       </c>
       <c r="V30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:23">
       <c r="B31">
         <v>8</v>
       </c>
@@ -2239,7 +2815,7 @@
         <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G31">
         <v>201</v>
@@ -2266,13 +2842,13 @@
         <v>377</v>
       </c>
       <c r="S31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:23">
       <c r="B32">
         <v>65</v>
       </c>
@@ -2319,13 +2895,13 @@
         <v>54</v>
       </c>
       <c r="S32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W32">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23">
       <c r="B33">
         <v>66</v>
       </c>
@@ -2363,7 +2939,7 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P33">
         <v>36003</v>
@@ -2372,16 +2948,16 @@
         <v>54</v>
       </c>
       <c r="S33" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W33">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23">
       <c r="B34">
         <v>60</v>
       </c>
@@ -2431,16 +3007,16 @@
         <v>68</v>
       </c>
       <c r="U34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W34">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:23">
       <c r="B35">
         <v>61</v>
       </c>
@@ -2487,19 +3063,19 @@
         <v>54</v>
       </c>
       <c r="S35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="W35">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:23">
       <c r="B36">
         <v>9</v>
       </c>
@@ -2513,7 +3089,7 @@
         <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G36">
         <v>110</v>
@@ -2546,7 +3122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23">
       <c r="B37">
         <v>85</v>
       </c>
@@ -2560,7 +3136,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G37">
         <v>3123</v>
@@ -2593,13 +3169,13 @@
         <v>61</v>
       </c>
       <c r="T37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W37">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23">
       <c r="B38">
         <v>167</v>
       </c>
@@ -2613,7 +3189,7 @@
         <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G38">
         <v>3108</v>
@@ -2646,13 +3222,13 @@
         <v>54</v>
       </c>
       <c r="S38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W38">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23">
       <c r="B39">
         <v>72</v>
       </c>
@@ -2690,13 +3266,13 @@
         <v>54</v>
       </c>
       <c r="S39" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:23">
       <c r="B40">
         <v>9000</v>
       </c>
@@ -2710,7 +3286,7 @@
         <v>4</v>
       </c>
       <c r="F40" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G40">
         <v>-1</v>
@@ -2734,16 +3310,16 @@
         <v>1</v>
       </c>
       <c r="R40" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S40" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W40">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:23">
       <c r="B41">
         <v>9003</v>
       </c>
@@ -2757,7 +3333,7 @@
         <v>5</v>
       </c>
       <c r="F41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G41">
         <v>-1</v>
@@ -2781,16 +3357,16 @@
         <v>1</v>
       </c>
       <c r="R41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="S41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23">
       <c r="B42">
         <v>182</v>
       </c>
@@ -2837,7 +3413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:23">
       <c r="B43">
         <v>77</v>
       </c>
@@ -2884,7 +3460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23">
       <c r="B44">
         <v>74</v>
       </c>
@@ -2931,7 +3507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23">
       <c r="B45">
         <v>81</v>
       </c>
@@ -2978,7 +3554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23">
       <c r="B46">
         <v>82</v>
       </c>
@@ -3025,7 +3601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23">
       <c r="B47">
         <v>88</v>
       </c>
@@ -3039,7 +3615,7 @@
         <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G47">
         <v>3127</v>
@@ -3069,13 +3645,13 @@
         <v>54</v>
       </c>
       <c r="S47" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="W47">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23">
       <c r="B48">
         <v>91</v>
       </c>
@@ -3089,7 +3665,7 @@
         <v>20</v>
       </c>
       <c r="F48" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G48">
         <v>-1</v>
@@ -3116,13 +3692,13 @@
         <v>54</v>
       </c>
       <c r="S48" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W48">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:23">
       <c r="B49">
         <v>89</v>
       </c>
@@ -3136,7 +3712,7 @@
         <v>21</v>
       </c>
       <c r="F49" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G49">
         <v>-1</v>
@@ -3172,16 +3748,16 @@
         <v>54</v>
       </c>
       <c r="S49" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="V49" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="W49">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:23">
       <c r="B50">
         <v>70</v>
       </c>
@@ -3195,7 +3771,7 @@
         <v>22</v>
       </c>
       <c r="F50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G50">
         <v>204</v>
@@ -3228,7 +3804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:23">
       <c r="B51">
         <v>166</v>
       </c>
@@ -3242,7 +3818,7 @@
         <v>23</v>
       </c>
       <c r="F51" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G51">
         <v>20172</v>
@@ -3266,7 +3842,7 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P51">
         <v>40013</v>
@@ -3278,16 +3854,16 @@
         <v>64</v>
       </c>
       <c r="T51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U51" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="W51">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:23">
       <c r="B52">
         <v>33</v>
       </c>
@@ -3301,7 +3877,7 @@
         <v>4</v>
       </c>
       <c r="F52" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G52">
         <v>208</v>
@@ -3325,10 +3901,10 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V52">
         <v>-9999</v>
@@ -3337,7 +3913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:23">
       <c r="B53">
         <v>20</v>
       </c>
@@ -3351,7 +3927,7 @@
         <v>4</v>
       </c>
       <c r="F53" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G53">
         <v>208</v>
@@ -3384,7 +3960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:23">
       <c r="B54">
         <v>93</v>
       </c>
@@ -3419,7 +3995,7 @@
         <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P54">
         <v>40007</v>
@@ -3434,7 +4010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:23">
       <c r="B55">
         <v>127</v>
       </c>
@@ -3469,7 +4045,7 @@
         <v>1</v>
       </c>
       <c r="O55" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P55">
         <v>40001</v>
@@ -3478,7 +4054,7 @@
         <v>57</v>
       </c>
       <c r="R55" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="S55" t="s">
         <v>64</v>
@@ -3487,7 +4063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:23">
       <c r="B56">
         <v>174</v>
       </c>
@@ -3531,7 +4107,7 @@
         <v>59</v>
       </c>
       <c r="R56" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="S56" t="s">
         <v>64</v>
@@ -3540,7 +4116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:23">
       <c r="B57">
         <v>175</v>
       </c>
@@ -3584,7 +4160,7 @@
         <v>40017</v>
       </c>
       <c r="R57" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="S57" t="s">
         <v>64</v>
@@ -3593,7 +4169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:23">
       <c r="B58">
         <v>172</v>
       </c>
@@ -3646,7 +4222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:23">
       <c r="B59">
         <v>162</v>
       </c>
@@ -3690,7 +4266,7 @@
         <v>77</v>
       </c>
       <c r="R59" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="S59" t="s">
         <v>64</v>
@@ -3699,7 +4275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:23">
       <c r="B60">
         <v>171</v>
       </c>
@@ -3752,7 +4328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:23">
       <c r="B61">
         <v>165</v>
       </c>
@@ -3787,7 +4363,7 @@
         <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P61">
         <v>40012</v>
@@ -3799,16 +4375,16 @@
         <v>64</v>
       </c>
       <c r="T61" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U61" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="W61">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:23">
       <c r="B62">
         <v>23</v>
       </c>
@@ -3822,7 +4398,7 @@
         <v>4</v>
       </c>
       <c r="F62" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G62">
         <v>208</v>
@@ -3855,7 +4431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:23">
       <c r="B63">
         <v>95</v>
       </c>
@@ -3890,7 +4466,7 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P63">
         <v>40007</v>
@@ -3905,7 +4481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:23">
       <c r="B64">
         <v>161</v>
       </c>
@@ -3949,7 +4525,7 @@
         <v>72</v>
       </c>
       <c r="R64" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="S64" t="s">
         <v>64</v>
@@ -3958,7 +4534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:23">
       <c r="B65">
         <v>176</v>
       </c>
@@ -4002,7 +4578,7 @@
         <v>40018</v>
       </c>
       <c r="R65" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="S65" t="s">
         <v>64</v>
@@ -4011,7 +4587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:23">
       <c r="B66">
         <v>128</v>
       </c>
@@ -4046,7 +4622,7 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P66">
         <v>40001</v>
@@ -4055,7 +4631,7 @@
         <v>57</v>
       </c>
       <c r="R66" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="S66" t="s">
         <v>64</v>
@@ -4064,7 +4640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23">
       <c r="B67">
         <v>24</v>
       </c>
@@ -4078,7 +4654,7 @@
         <v>4</v>
       </c>
       <c r="F67" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G67">
         <v>208</v>
@@ -4111,7 +4687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:23">
       <c r="B68">
         <v>96</v>
       </c>
@@ -4146,7 +4722,7 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P68">
         <v>40007</v>
@@ -4161,7 +4737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:23">
       <c r="B69">
         <v>129</v>
       </c>
@@ -4196,7 +4772,7 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P69">
         <v>40001</v>
@@ -4205,7 +4781,7 @@
         <v>57</v>
       </c>
       <c r="R69" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="S69" t="s">
         <v>64</v>
@@ -4214,7 +4790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:23">
       <c r="B70">
         <v>25</v>
       </c>
@@ -4228,7 +4804,7 @@
         <v>4</v>
       </c>
       <c r="F70" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G70">
         <v>208</v>
@@ -4261,7 +4837,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:23">
       <c r="B71">
         <v>26</v>
       </c>
@@ -4275,7 +4851,7 @@
         <v>4</v>
       </c>
       <c r="F71" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G71">
         <v>208</v>
@@ -4308,7 +4884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:23">
       <c r="B72">
         <v>27</v>
       </c>
@@ -4322,7 +4898,7 @@
         <v>4</v>
       </c>
       <c r="F72" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G72">
         <v>208</v>
@@ -4355,7 +4931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23">
       <c r="B73">
         <v>28</v>
       </c>
@@ -4369,7 +4945,7 @@
         <v>4</v>
       </c>
       <c r="F73" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G73">
         <v>208</v>
@@ -4402,7 +4978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:23">
       <c r="B74">
         <v>29</v>
       </c>
@@ -4416,7 +4992,7 @@
         <v>4</v>
       </c>
       <c r="F74" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G74">
         <v>208</v>
@@ -4449,7 +5025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:23">
       <c r="B75">
         <v>30</v>
       </c>
@@ -4463,7 +5039,7 @@
         <v>4</v>
       </c>
       <c r="F75" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G75">
         <v>208</v>
@@ -4496,7 +5072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:23">
       <c r="B76">
         <v>31</v>
       </c>
@@ -4510,7 +5086,7 @@
         <v>4</v>
       </c>
       <c r="F76" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G76">
         <v>208</v>
@@ -4543,7 +5119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23">
       <c r="B77">
         <v>32</v>
       </c>
@@ -4557,7 +5133,7 @@
         <v>4</v>
       </c>
       <c r="F77" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G77">
         <v>208</v>
@@ -4590,7 +5166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:23">
       <c r="B78">
         <v>178</v>
       </c>
@@ -4604,7 +5180,7 @@
         <v>5</v>
       </c>
       <c r="F78" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G78">
         <v>21000</v>
@@ -4631,13 +5207,13 @@
         <v>0</v>
       </c>
       <c r="S78" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W78">
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:23">
       <c r="B79">
         <v>179</v>
       </c>
@@ -4672,13 +5248,13 @@
         <v>0</v>
       </c>
       <c r="S79" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W79">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23">
       <c r="B80">
         <v>180</v>
       </c>
@@ -4713,16 +5289,16 @@
         <v>0</v>
       </c>
       <c r="R80" t="s">
+        <v>121</v>
+      </c>
+      <c r="S80" t="s">
         <v>120</v>
       </c>
-      <c r="S80" t="s">
-        <v>119</v>
-      </c>
       <c r="W80">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:23">
       <c r="B81">
         <v>181</v>
       </c>
@@ -4757,13 +5333,13 @@
         <v>1</v>
       </c>
       <c r="S81" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W81">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:23">
       <c r="B82">
         <v>205</v>
       </c>
@@ -4777,7 +5353,7 @@
         <v>5</v>
       </c>
       <c r="F82" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G82">
         <v>21000</v>
@@ -4804,13 +5380,13 @@
         <v>0</v>
       </c>
       <c r="S82" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W82">
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:23">
       <c r="B83">
         <v>206</v>
       </c>
@@ -4845,13 +5421,13 @@
         <v>0</v>
       </c>
       <c r="S83" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W83">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:23">
       <c r="B84">
         <v>207</v>
       </c>
@@ -4886,16 +5462,16 @@
         <v>0</v>
       </c>
       <c r="R84" t="s">
+        <v>121</v>
+      </c>
+      <c r="S84" t="s">
         <v>120</v>
       </c>
-      <c r="S84" t="s">
-        <v>119</v>
-      </c>
       <c r="W84">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:23">
       <c r="B85">
         <v>208</v>
       </c>
@@ -4930,13 +5506,13 @@
         <v>1</v>
       </c>
       <c r="S85" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W85">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:23">
       <c r="B86">
         <v>218</v>
       </c>
@@ -4950,7 +5526,7 @@
         <v>5</v>
       </c>
       <c r="F86" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G86">
         <v>21000</v>
@@ -4977,13 +5553,13 @@
         <v>0</v>
       </c>
       <c r="S86" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W86">
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:23">
       <c r="B87">
         <v>219</v>
       </c>
@@ -5018,13 +5594,13 @@
         <v>0</v>
       </c>
       <c r="S87" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W87">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:23">
       <c r="B88">
         <v>220</v>
       </c>
@@ -5059,16 +5635,16 @@
         <v>0</v>
       </c>
       <c r="R88" t="s">
+        <v>121</v>
+      </c>
+      <c r="S88" t="s">
         <v>120</v>
       </c>
-      <c r="S88" t="s">
-        <v>119</v>
-      </c>
       <c r="W88">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:23">
       <c r="B89">
         <v>221</v>
       </c>
@@ -5103,13 +5679,13 @@
         <v>1</v>
       </c>
       <c r="S89" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W89">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:23">
       <c r="B90">
         <v>222</v>
       </c>
@@ -5123,7 +5699,7 @@
         <v>5</v>
       </c>
       <c r="F90" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G90">
         <v>21000</v>
@@ -5150,13 +5726,13 @@
         <v>0</v>
       </c>
       <c r="S90" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W90">
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:23">
       <c r="B91">
         <v>223</v>
       </c>
@@ -5191,13 +5767,13 @@
         <v>0</v>
       </c>
       <c r="S91" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W91">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:23">
       <c r="B92">
         <v>224</v>
       </c>
@@ -5232,16 +5808,16 @@
         <v>0</v>
       </c>
       <c r="R92" t="s">
+        <v>121</v>
+      </c>
+      <c r="S92" t="s">
         <v>120</v>
       </c>
-      <c r="S92" t="s">
-        <v>119</v>
-      </c>
       <c r="W92">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:23">
       <c r="B93">
         <v>225</v>
       </c>
@@ -5276,13 +5852,13 @@
         <v>1</v>
       </c>
       <c r="S93" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W93">
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:23">
       <c r="B94">
         <v>210</v>
       </c>
@@ -5296,7 +5872,7 @@
         <v>5</v>
       </c>
       <c r="F94" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G94">
         <v>21000</v>
@@ -5323,13 +5899,13 @@
         <v>0</v>
       </c>
       <c r="S94" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W94">
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:23">
       <c r="B95">
         <v>211</v>
       </c>
@@ -5364,13 +5940,13 @@
         <v>0</v>
       </c>
       <c r="S95" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W95">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:23">
       <c r="B96">
         <v>212</v>
       </c>
@@ -5405,16 +5981,16 @@
         <v>0</v>
       </c>
       <c r="R96" t="s">
+        <v>121</v>
+      </c>
+      <c r="S96" t="s">
         <v>120</v>
       </c>
-      <c r="S96" t="s">
-        <v>119</v>
-      </c>
       <c r="W96">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:23">
       <c r="B97">
         <v>213</v>
       </c>
@@ -5449,13 +6025,13 @@
         <v>1</v>
       </c>
       <c r="S97" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W97">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:23">
       <c r="B98">
         <v>214</v>
       </c>
@@ -5469,7 +6045,7 @@
         <v>5</v>
       </c>
       <c r="F98" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G98">
         <v>21000</v>
@@ -5496,13 +6072,13 @@
         <v>0</v>
       </c>
       <c r="S98" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W98">
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:23">
       <c r="B99">
         <v>215</v>
       </c>
@@ -5537,13 +6113,13 @@
         <v>0</v>
       </c>
       <c r="S99" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W99">
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:23">
       <c r="B100">
         <v>216</v>
       </c>
@@ -5578,16 +6154,16 @@
         <v>0</v>
       </c>
       <c r="R100" t="s">
+        <v>121</v>
+      </c>
+      <c r="S100" t="s">
         <v>120</v>
       </c>
-      <c r="S100" t="s">
-        <v>119</v>
-      </c>
       <c r="W100">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:23">
       <c r="B101">
         <v>217</v>
       </c>
@@ -5622,13 +6198,13 @@
         <v>1</v>
       </c>
       <c r="S101" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W101">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:23">
       <c r="B102">
         <v>226</v>
       </c>
@@ -5642,7 +6218,7 @@
         <v>5</v>
       </c>
       <c r="F102" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G102">
         <v>21000</v>
@@ -5669,13 +6245,13 @@
         <v>0</v>
       </c>
       <c r="S102" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W102">
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:23">
       <c r="B103">
         <v>227</v>
       </c>
@@ -5710,13 +6286,13 @@
         <v>0</v>
       </c>
       <c r="S103" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W103">
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:23">
       <c r="B104">
         <v>228</v>
       </c>
@@ -5751,16 +6327,16 @@
         <v>0</v>
       </c>
       <c r="R104" t="s">
+        <v>121</v>
+      </c>
+      <c r="S104" t="s">
         <v>120</v>
       </c>
-      <c r="S104" t="s">
-        <v>119</v>
-      </c>
       <c r="W104">
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:23">
       <c r="B105">
         <v>229</v>
       </c>
@@ -5795,13 +6371,13 @@
         <v>1</v>
       </c>
       <c r="S105" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W105">
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:23">
       <c r="B106">
         <v>230</v>
       </c>
@@ -5815,7 +6391,7 @@
         <v>5</v>
       </c>
       <c r="F106" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G106">
         <v>21000</v>
@@ -5842,13 +6418,13 @@
         <v>0</v>
       </c>
       <c r="S106" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W106">
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:23">
       <c r="B107">
         <v>231</v>
       </c>
@@ -5883,13 +6459,13 @@
         <v>0</v>
       </c>
       <c r="S107" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W107">
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:23">
       <c r="B108">
         <v>232</v>
       </c>
@@ -5924,16 +6500,16 @@
         <v>0</v>
       </c>
       <c r="R108" t="s">
+        <v>121</v>
+      </c>
+      <c r="S108" t="s">
         <v>120</v>
       </c>
-      <c r="S108" t="s">
-        <v>119</v>
-      </c>
       <c r="W108">
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:23">
       <c r="B109">
         <v>233</v>
       </c>
@@ -5968,13 +6544,13 @@
         <v>1</v>
       </c>
       <c r="S109" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W109">
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:23">
       <c r="B110">
         <v>300</v>
       </c>
@@ -5985,7 +6561,7 @@
         <v>6</v>
       </c>
       <c r="F110" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G110">
         <v>-1</v>
@@ -6012,13 +6588,13 @@
         <v>0</v>
       </c>
       <c r="S110" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="W110">
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:23">
       <c r="B111">
         <v>301</v>
       </c>
@@ -6032,7 +6608,7 @@
         <v>1</v>
       </c>
       <c r="F111" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G111">
         <v>-1</v>
@@ -6056,13 +6632,13 @@
         <v>0</v>
       </c>
       <c r="S111" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="W111">
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:23">
       <c r="B112">
         <v>302</v>
       </c>
@@ -6076,7 +6652,7 @@
         <v>2</v>
       </c>
       <c r="F112" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G112">
         <v>-1</v>
@@ -6100,16 +6676,16 @@
         <v>0</v>
       </c>
       <c r="R112" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S112" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="W112">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:23">
       <c r="B113">
         <v>303</v>
       </c>
@@ -6123,7 +6699,7 @@
         <v>3</v>
       </c>
       <c r="F113" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G113">
         <v>-1</v>
@@ -6153,7 +6729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:23">
       <c r="B114">
         <v>304</v>
       </c>
@@ -6167,7 +6743,7 @@
         <v>4</v>
       </c>
       <c r="F114" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G114">
         <v>-1</v>
@@ -6197,7 +6773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:23">
       <c r="B115">
         <v>305</v>
       </c>
@@ -6211,7 +6787,7 @@
         <v>5</v>
       </c>
       <c r="F115" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G115">
         <v>-1</v>
@@ -6235,16 +6811,16 @@
         <v>0</v>
       </c>
       <c r="R115" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S115" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="W115">
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:23">
       <c r="B116">
         <v>306</v>
       </c>
@@ -6258,7 +6834,7 @@
         <v>6</v>
       </c>
       <c r="F116" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G116">
         <v>-1</v>
@@ -6282,16 +6858,16 @@
         <v>0</v>
       </c>
       <c r="R116" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S116" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="W116">
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:23">
       <c r="B117">
         <v>307</v>
       </c>
@@ -6305,7 +6881,7 @@
         <v>7</v>
       </c>
       <c r="F117" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G117">
         <v>-1</v>
@@ -6329,16 +6905,16 @@
         <v>0</v>
       </c>
       <c r="R117" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S117" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="W117">
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:23">
       <c r="B118">
         <v>308</v>
       </c>
@@ -6352,7 +6928,7 @@
         <v>8</v>
       </c>
       <c r="F118" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G118">
         <v>-1</v>
@@ -6376,16 +6952,16 @@
         <v>0</v>
       </c>
       <c r="R118" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S118" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="W118">
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:23">
       <c r="B119">
         <v>309</v>
       </c>
@@ -6399,7 +6975,7 @@
         <v>9</v>
       </c>
       <c r="F119" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G119">
         <v>-1</v>
@@ -6423,16 +6999,16 @@
         <v>0</v>
       </c>
       <c r="R119" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S119" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="W119">
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:23">
       <c r="B120">
         <v>310</v>
       </c>
@@ -6446,7 +7022,7 @@
         <v>10</v>
       </c>
       <c r="F120" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G120">
         <v>-1</v>
@@ -6470,16 +7046,16 @@
         <v>0</v>
       </c>
       <c r="R120" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S120" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="W120">
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:23">
       <c r="B121">
         <v>311</v>
       </c>
@@ -6493,7 +7069,7 @@
         <v>11</v>
       </c>
       <c r="F121" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G121">
         <v>-1</v>
@@ -6517,16 +7093,16 @@
         <v>0</v>
       </c>
       <c r="R121" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S121" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="W121">
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:23">
       <c r="B122">
         <v>312</v>
       </c>
@@ -6540,7 +7116,7 @@
         <v>12</v>
       </c>
       <c r="F122" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G122">
         <v>-1</v>
@@ -6564,16 +7140,16 @@
         <v>0</v>
       </c>
       <c r="R122" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S122" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="W122">
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:23">
       <c r="B123">
         <v>313</v>
       </c>
@@ -6587,7 +7163,7 @@
         <v>13</v>
       </c>
       <c r="F123" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G123">
         <v>-1</v>
@@ -6611,16 +7187,16 @@
         <v>0</v>
       </c>
       <c r="R123" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S123" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="W123">
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:23">
       <c r="B124">
         <v>314</v>
       </c>
@@ -6634,7 +7210,7 @@
         <v>14</v>
       </c>
       <c r="F124" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G124">
         <v>-1</v>
@@ -6658,16 +7234,16 @@
         <v>0</v>
       </c>
       <c r="R124" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S124" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="W124">
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:23">
       <c r="B125">
         <v>315</v>
       </c>
@@ -6681,7 +7257,7 @@
         <v>15</v>
       </c>
       <c r="F125" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G125">
         <v>-1</v>
@@ -6705,16 +7281,16 @@
         <v>0</v>
       </c>
       <c r="R125" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S125" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="W125">
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:23">
       <c r="B126">
         <v>316</v>
       </c>
@@ -6728,7 +7304,7 @@
         <v>16</v>
       </c>
       <c r="F126" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G126">
         <v>-1</v>
@@ -6752,16 +7328,16 @@
         <v>0</v>
       </c>
       <c r="R126" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S126" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="W126">
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:23">
       <c r="B127">
         <v>400</v>
       </c>
@@ -6775,7 +7351,7 @@
         <v>7</v>
       </c>
       <c r="F127" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G127">
         <v>-1</v>
@@ -6802,7 +7378,7 @@
         <v>1</v>
       </c>
       <c r="R127" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="S127" t="s">
         <v>66</v>
@@ -6811,7 +7387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:23">
       <c r="B128">
         <v>15</v>
       </c>
@@ -6825,7 +7401,7 @@
         <v>10</v>
       </c>
       <c r="F128" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G128">
         <v>261</v>
@@ -6849,13 +7425,13 @@
         <v>1</v>
       </c>
       <c r="S128" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="W128">
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:23">
       <c r="B129">
         <v>68</v>
       </c>
@@ -6908,7 +7484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:23">
       <c r="B130">
         <v>69</v>
       </c>
@@ -6961,7 +7537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:23">
       <c r="B131">
         <v>1000</v>
       </c>
@@ -6975,7 +7551,7 @@
         <v>99</v>
       </c>
       <c r="F131" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G131">
         <v>2026</v>
@@ -7008,7 +7584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:23">
       <c r="B132">
         <v>5</v>
       </c>
@@ -7022,7 +7598,7 @@
         <v>100</v>
       </c>
       <c r="F132" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G132">
         <v>2026</v>
@@ -7052,7 +7628,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:23">
       <c r="B133">
         <v>2</v>
       </c>
@@ -7066,7 +7642,7 @@
         <v>101</v>
       </c>
       <c r="F133" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G133">
         <v>206</v>
@@ -7090,13 +7666,13 @@
         <v>1</v>
       </c>
       <c r="S133" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W133">
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:23">
       <c r="B134">
         <v>22</v>
       </c>
@@ -7110,7 +7686,7 @@
         <v>102</v>
       </c>
       <c r="F134" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G134">
         <v>234</v>
@@ -7140,7 +7716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:23">
       <c r="B135">
         <v>177</v>
       </c>
@@ -7154,7 +7730,7 @@
         <v>103</v>
       </c>
       <c r="F135" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G135">
         <v>20260</v>
@@ -7187,13 +7763,13 @@
         <v>54</v>
       </c>
       <c r="S135" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W135">
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:23">
       <c r="B136">
         <v>19</v>
       </c>
@@ -7207,7 +7783,7 @@
         <v>104</v>
       </c>
       <c r="F136" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G136">
         <v>2027</v>
@@ -7237,7 +7813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:23">
       <c r="B137">
         <v>21</v>
       </c>
@@ -7251,7 +7827,7 @@
         <v>105</v>
       </c>
       <c r="F137" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G137">
         <v>99891</v>
@@ -7284,7 +7860,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:23">
       <c r="B138">
         <v>13</v>
       </c>
@@ -7298,7 +7874,7 @@
         <v>999</v>
       </c>
       <c r="F138" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G138">
         <v>-1</v>
@@ -7322,13 +7898,13 @@
         <v>1</v>
       </c>
       <c r="S138" t="s">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="W138">
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:23">
       <c r="B139">
         <v>9002</v>
       </c>
@@ -7339,7 +7915,7 @@
         <v>1000</v>
       </c>
       <c r="F139" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G139">
         <v>-1</v>
@@ -7366,13 +7942,13 @@
         <v>0</v>
       </c>
       <c r="S139" t="s">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="W139">
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:23">
       <c r="B140">
         <v>1202</v>
       </c>
@@ -7383,7 +7959,7 @@
         <v>1001</v>
       </c>
       <c r="F140" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G140">
         <v>-1</v>
@@ -7416,7 +7992,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:23">
       <c r="B141">
         <v>9001</v>
       </c>
@@ -7427,7 +8003,7 @@
         <v>1002</v>
       </c>
       <c r="F141" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G141">
         <v>-1</v>
@@ -7454,13 +8030,13 @@
         <v>0</v>
       </c>
       <c r="S141" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W141">
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:23">
       <c r="B142">
         <v>1201</v>
       </c>
@@ -7471,7 +8047,7 @@
         <v>1003</v>
       </c>
       <c r="F142" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G142">
         <v>-1</v>
@@ -7498,13 +8074,13 @@
         <v>0</v>
       </c>
       <c r="S142" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="W142">
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:23">
       <c r="B143">
         <v>9017</v>
       </c>
@@ -7515,7 +8091,7 @@
         <v>1004</v>
       </c>
       <c r="F143" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G143">
         <v>-1</v>
@@ -7542,13 +8118,13 @@
         <v>0</v>
       </c>
       <c r="S143" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="W143">
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:23">
       <c r="B144">
         <v>9015</v>
       </c>
@@ -7562,7 +8138,7 @@
         <v>2000</v>
       </c>
       <c r="F144" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G144">
         <v>-1</v>
@@ -7589,13 +8165,13 @@
         <v>0</v>
       </c>
       <c r="S144" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W144">
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:23">
       <c r="B145">
         <v>9016</v>
       </c>
@@ -7609,7 +8185,7 @@
         <v>2001</v>
       </c>
       <c r="F145" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G145">
         <v>-1</v>
@@ -7643,7 +8219,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/data_execl/base_data/ActivityGroups.xlsx
+++ b/data_execl/base_data/ActivityGroups.xlsx
@@ -512,14 +512,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -977,28 +970,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1007,118 +1003,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1450,6 +1443,16 @@
   <sheetPr/>
   <dimension ref="A1:W145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="6" max="6" width="23.5089285714286" customWidth="1"/>
+    <col min="7" max="7" width="19.4910714285714" customWidth="1"/>
+    <col min="8" max="8" width="26.4821428571429" customWidth="1"/>
+    <col min="9" max="9" width="20.6875" customWidth="1"/>
+    <col min="10" max="10" width="21.7232142857143" customWidth="1"/>
+    <col min="11" max="11" width="16.2232142857143" customWidth="1"/>
+    <col min="12" max="12" width="13.2321428571429" customWidth="1"/>
+    <col min="13" max="13" width="11.3125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="2:23">
       <c r="B1" t="s">
@@ -6591,7 +6594,7 @@
         <v>125</v>
       </c>
       <c r="W110">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111" spans="2:23">
@@ -7625,7 +7628,7 @@
         <v>56</v>
       </c>
       <c r="W132">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133" spans="2:23">
@@ -7669,7 +7672,7 @@
         <v>75</v>
       </c>
       <c r="W133">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="2:23">
